--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -512,22 +512,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -512,22 +512,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -517,17 +517,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,25 +1025,79 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Central, HK, HK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Seoul, KR, 100768</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IT, Data &amp; Analytics</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,25 +1079,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,22 +539,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,17 +571,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,22 +566,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,12 +539,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -566,12 +566,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -598,17 +598,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -517,98 +517,98 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,10 +1121,64 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Central, HK, HK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Seoul, KR, 100768</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,12 +593,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,12 +593,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -593,22 +593,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -593,27 +593,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,25 +1160,52 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -625,17 +625,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,12 +620,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,17 +1138,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -620,22 +620,22 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,17 +706,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,44 +625,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,10 +1202,37 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Share analytics</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -647,22 +647,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,17 +733,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -652,17 +652,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,44 +652,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,25 +1214,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -674,22 +674,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -674,12 +674,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -674,49 +674,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,12 +728,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,25 +1241,52 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Seoul, KR, 100768</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -701,22 +701,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -701,12 +701,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -701,49 +701,49 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,25 +1268,52 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -728,22 +728,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -517,7 +517,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -527,12 +527,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,10 +1310,37 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Risk, Regulatory &amp; Forensic</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,12 +1187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,17 +841,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -755,39 +755,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,17 +895,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,10 +1337,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Managing risk</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,17 +1057,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,12 +809,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,12 +1052,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,22 +782,22 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,12 +836,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1052,22 +1052,22 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -782,27 +782,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
@@ -814,17 +814,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,12 +1349,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1364,10 +1364,37 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Nomura</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Singapore, SG, 018983</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -809,22 +809,22 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,12 +917,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -976,17 +976,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -998,22 +998,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,12 +1241,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -473,12 +473,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -490,22 +490,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -598,7 +598,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -625,22 +625,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -733,22 +733,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,44 +814,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1187,22 +1187,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1219,17 +1219,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1241,22 +1241,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,12 +1295,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1381,20 +1381,47 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HSBC and Quantum</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Check site</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,12 +1106,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,22 +1133,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-117372/1381208600/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -836,22 +836,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -868,17 +868,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,12 +890,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,22 +944,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk Management</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,12 +971,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,22 +1079,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1106,22 +1106,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,22 +1214,22 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,12 +1268,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1295,22 +1295,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,22 +463,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Stress Testing AnalystStress Testing AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Stress-Testing-Analyst-018983/1408508600/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>VP, Market Risk ManagerVP, Market Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +500,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-VP%2C-Market-Risk-Manager-HK/1407514100/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -517,22 +517,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Associate, Quantitative StrategistAssociate, Quantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Associate%2C-Quantitative-Strategist-HK/1405560100/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
@@ -544,22 +544,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1403543100/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -571,22 +571,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Market Risk Manager (Hong Kong)Associate, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Associate%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -598,22 +598,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
+          <t>Risk HQ AnalystRisk HQ AnalystRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-HQ-Analyst-018983/1400117200/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Management Information &amp; Data Analytics Vice PresidentManagement Information &amp; Data Analytics Vice PresidentFinanceCentral, HK, HKFinance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Management-Information-&amp;-Data-Analytics-Vice-President-HK/1398810500/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
+          <t>Global Market Risk and Control AssociateGlobal Market Risk and Control AssociateGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Global-Market-Risk-and-Control-Associate-HK/1397091000/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
+          <t>Client Reporting and Performance Analytics AssociateClient Reporting and Performance Analytics AssociateOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Client-Reporting-and-Performance-Analytics-Associate-018983/1396215400/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
+          <t>Quantitative StrategistQuantitative StrategistGlobal MarketsCentral, HK, HKInstinet</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
+          <t>https://careers.nomura.com/Instinet/job/Central-Quantitative-Strategist-HK/1386837600/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-018983/1381208300/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
+          <t>Risk &amp; Control Executive DirectorRisk &amp; Control Executive DirectorOperationsSingapore, SG, 018983Operations</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-&amp;-Control-Executive-Director-018983/1381208600/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
     </row>
@@ -787,22 +787,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
+          <t>Algo Risk &amp; ControlAlgo Risk &amp; ControlGlobal MarketsCentral, HK, HKGlobal Markets</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Singapore, SG, 117372</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Algo-Risk-&amp;-Control-HK/1341158000/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
     </row>
@@ -841,44 +841,44 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>Risk and Control Vice PresidentRisk and Control Vice PresidentOperationsSingapore, SG, 117372Operations</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 117372</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Risk-and-Control-Vice-President-117372/1381208300/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk Management</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,22 +1160,22 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,25 +1403,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>Central, HK, HK</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Risk Management</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
           <t>Check site</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://careers.mufgamericas.com/risk-management-summer-analyst-program</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
+          <t>HSBC and Quantum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IT, Data &amp; Analytics</t>
+          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Seoul, KR, 100768</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
+          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KPMG</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Risk and Regulation</t>
+          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
+          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Managing risk</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1025,22 +1025,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1079,12 +1079,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
+          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
+          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Central, HK, HK</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1133,12 +1133,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>KPMG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Share analytics</t>
+          <t>Risk and Regulation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
+          <t>https://home.kpmg/xx/en/home/careers.html/xx/en/our-insights/risk-and-regulation.html</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1160,12 +1160,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1192,17 +1192,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Associate, Market Risk Manager (Singapore)Associate, Market Risk Manager (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
+          <t>Vice President, Market Risk Manager (Hong Kong)Vice President, Market Risk Manager (Hong Kong)Risk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Market-Risk-Manager-%28Singapore%29-018983/1369025100/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Vice-President%2C-Market-Risk-Manager-%28Hong-Kong%29-HK/1369438000/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1214,12 +1214,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>From Hackathon to Higher Ed: The BlackRock for Universities StoryBlackRock for Universities began as Sam Konigsberg's hackathon idea in 2019. It became a reality, providing students with industry-leading tools for better portfolio management. By integrating Aladdin, students can analyze their portfolios more effectively, focusing on risk and intentionality, thus bridging the gap between academic learning and professional investment practices.Read more</t>
+          <t>Risk, Regulatory &amp; Forensic</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://careers.blackrock.com/from-hackathon-to-higher-ed-the-blackrock-for-universities-story</t>
+          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=bn_deloitte-forensic</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Associate, Treasury Risk ManagerAssociate, Treasury Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Associate, Stress Testing Analyst (Singapore)Associate, Stress Testing Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Treasury-Risk-Manager-018983/1348705700/</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Stress-Testing-Analyst-%28Singapore%29-018983/1373943000/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1268,22 +1268,22 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1369436100/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementSingapore, SG, 018983Risk</t>
+          <t>Operational Risk ManagerOperational Risk ManagerRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Operational-Risk-Manager-018983/1361397800/</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Operational-Risk-Manager-HK/1364644500/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1322,22 +1322,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+          <t>Managing risk</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Singapore, SG, 018983</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-AI-Data-Scientist-%28Singapore%29-018983/1345756000/</t>
+          <t>https://www.hsbc.com/careers/who-we-are/esg-and-responsible-business/managing-risk</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1349,22 +1349,22 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1376,22 +1376,22 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1403,22 +1403,22 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">

--- a/Job_Listings_Master.xlsx
+++ b/Job_Listings_Master.xlsx
@@ -863,22 +863,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HSBC</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HSBC and Quantum</t>
+          <t>Team Lead, Hedge Fund Credit RiskTeam Lead, Hedge Fund Credit RiskRisk ManagementCentral, HK, HKRisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Central, HK, HK</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.hsbc.com/careers/who-we-are/hsbc-and-digital/hsbc-and-quantum</t>
+          <t>https://careers.nomura.com/Nomura/job/Central-Team-Lead%2C-Hedge-Fund-Credit-Risk-HK/1368182600/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -890,22 +890,22 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Nomura</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risk, Regulatory &amp; Forensic</t>
+          <t>Associate, Credit Risk Analyst (Singapore)Associate, Credit Risk Analyst (Singapore)Risk ManagementSingapore, SG, 018983Risk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Check site</t>
+          <t>Singapore, SG, 018983</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://jobs.deloitte.com/global/en/services/consulting/services/risk-regulatory-forensic.html?icid=top_deloitte-forensic</t>
+          <t>https://careers.nomura.com/Nomura/job/Singapore-Associate%2C-Credit-Risk-Analyst-%28Singapore%29-018983/1367269900/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -917,22 +917,22 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Market Risk ManagerMarket Risk ManagerRisk ManagementSeoul, KR, 100768Risk</t>
+          <t>IT, Data &amp; Analytics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seoul, KR, 100768</t>
+          <t>Check site</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://careers.nomura.com/Nomura/job/Seoul-Market-Risk-Manager-100768/1373483900/</t>
+          <t>https://jobs.deloitte.com/global/en/services/audit-assurance/services/it-data-analytics.html?icid=top_it-data-analytics</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiskIdentifies, monitors, evaluates, and manages the firm’s financial and non-financial risks in support of the firm’s strategic plan.</t>
+          <t>Share analytics</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/careers/our-firm/risk</t>
+          <t>https://www.hsbc.com/careers/investors/shareholder-and-dividend-information/share-analytics</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -971,22 +971,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nomura</t>
+          <t>HSBC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Associate, AI Data Scientist (Singapore)Associate, AI Data Scientist (Singapore)Group TechnologySingapore, SG, 018983IT\Technology</t>
+